--- a/resources/residence/residence_temple.xlsx
+++ b/resources/residence/residence_temple.xlsx
@@ -1,13 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\workspace_art_client\GameConfig\data_table\normal\residence\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F663919E-FB1E-4014-97F8-549500CA37CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ResidenceTemple" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CONFIG" sheetId="1" r:id="rId1"/>
+    <sheet name="ResidenceTemple" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="1" hidden="1">ResidenceTemple!#REF!</definedName>
@@ -233,101 +240,424 @@
     <definedName name="Z_FAF1ADB8_46A9_40B0_AA1B_9C75E39038F2_.wvu.FilterData" localSheetId="1" hidden="1">ResidenceTemple!#REF!</definedName>
     <definedName name="Z_FF6A625A_6008_4A1D_8FF0_F8A30B9F02A0_.wvu.FilterData" localSheetId="1" hidden="1">ResidenceTemple!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>梁中量</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>梁中量:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+不允许跳过</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>梁中量:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+combat.xls</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>梁中量:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+这里可以更换土地庙模型</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>梁中量:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+显示用，不真实投放</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+  <si>
+    <t>表名</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>列作用说明</t>
+  </si>
+  <si>
+    <t>生成文件</t>
+  </si>
+  <si>
+    <t>导出目标</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要导出的sheet</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>导出文件</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SERVER</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLIENT</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>name:string</t>
+  </si>
+  <si>
+    <t>种子名称</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc:string</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>id:int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡id</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗id</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>所需洞府等级</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>residence_level:int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>building_item_id:int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>土地庙建筑id</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>combat_id:int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>residence/residence_temple.py</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResidenceTemple</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>洞府土地庙建筑配置</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡4</t>
+  </si>
+  <si>
+    <t>关卡5</t>
+  </si>
+  <si>
+    <t>关卡6</t>
+  </si>
+  <si>
+    <t>关卡7</t>
+  </si>
+  <si>
+    <t>关卡8</t>
+  </si>
+  <si>
+    <t>关卡9</t>
+  </si>
+  <si>
+    <t>特殊道具id</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>special_item_id:int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡1-1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡1-2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡1-3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡2-1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡2-2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡2-3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡2-4</t>
+  </si>
+  <si>
+    <t>关卡2-5</t>
+  </si>
+  <si>
+    <t>关卡10</t>
+  </si>
+  <si>
+    <t>关卡1-4</t>
+  </si>
+  <si>
+    <t>关卡1-5</t>
+  </si>
+  <si>
+    <t>icon:string</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡图标</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>XGUI/res/round/Residence/icon/temple_01.png</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>XGUI/res/round/Residence/icon/temple_02.png</t>
+  </si>
+  <si>
+    <t>XGUI/res/round/Residence/icon/temple_03.png</t>
+  </si>
+  <si>
+    <t>XGUI/res/round/Residence/icon/temple_04.png</t>
+  </si>
+  <si>
+    <t>XGUI/res/round/Residence/icon/temple_05.png</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color indexed="8"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="2"/>
-      <color indexed="8"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="2"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color indexed="81"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color indexed="81"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color indexed="81"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -363,102 +693,99 @@
     </border>
   </borders>
   <cellStyleXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="9"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="9"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="9" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1"/>
-    <cellStyle name="常规 2 2" xfId="2"/>
-    <cellStyle name="常规 2 3" xfId="3"/>
-    <cellStyle name="常规 2" xfId="4"/>
-    <cellStyle name="常规 3" xfId="5"/>
-    <cellStyle name="常规 4" xfId="6"/>
-    <cellStyle name="常规 5" xfId="7"/>
-    <cellStyle name="常规_CONFIG" xfId="8"/>
-    <cellStyle name="常规_Sheet1" xfId="9"/>
-    <cellStyle name="常规 7" xfId="10"/>
-    <cellStyle name="常规 11" xfId="11"/>
+    <cellStyle name="常规 11" xfId="11" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="常规 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="常规 2 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="常规 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="常规 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="常规 5" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="常规 7" xfId="10" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="常规_CONFIG" xfId="8" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="常规_Sheet1" xfId="9" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
@@ -513,109 +840,15 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>梁中量</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>梁中量:
-不允许跳过</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>梁中量:
-combat.xls</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>梁中量:
-这里可以更换土地庙模型</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>梁中量:
-显示用，不真实投放</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -875,608 +1108,456 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="21.125" customWidth="1" style="8" min="1" max="1"/>
-    <col width="56.125" customWidth="1" style="8" min="2" max="2"/>
-    <col width="49.5" customWidth="1" style="8" min="3" max="3"/>
-    <col width="43.875" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
-    <col width="23.5" customWidth="1" style="8" min="5" max="5"/>
-    <col width="19.25" customWidth="1" style="8" min="6" max="6"/>
-    <col width="21.375" customWidth="1" style="8" min="8" max="8"/>
+    <col min="1" max="1" width="21.125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="56.125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="49.5" style="8" customWidth="1"/>
+    <col min="4" max="4" width="43.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.5" style="8" customWidth="1"/>
+    <col min="6" max="6" width="19.25" style="8" customWidth="1"/>
+    <col min="8" max="8" width="21.375" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="8">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>表名</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>洞府土地庙建筑配置</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" s="8">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="16.5" customHeight="1" s="8">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>列作用说明</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>导出目标</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>需要导出的sheet</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>导出文件</t>
-        </is>
-      </c>
-      <c r="F3" s="0" t="n"/>
-      <c r="H3" s="0" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>生成文件</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>ResidenceTemple</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>residence/residence_temple.py</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>CLIENT</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>ResidenceTemple</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>residence/residence_temple.py</t>
-        </is>
+    <row r="1" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="4"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3"/>
+      <c r="G3" s="8"/>
+      <c r="H3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="B5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
-    <col width="17" customWidth="1" style="9" min="2" max="2"/>
-    <col width="34.625" customWidth="1" style="9" min="3" max="3"/>
-    <col width="17" customWidth="1" style="9" min="4" max="7"/>
-    <col width="58.25" customWidth="1" style="9" min="8" max="8"/>
-    <col width="9" customWidth="1" style="13" min="9" max="16384"/>
+    <col min="1" max="1" width="16.75" style="9" customWidth="1"/>
+    <col min="2" max="2" width="17" style="9" customWidth="1"/>
+    <col min="3" max="3" width="34.625" style="9" customWidth="1"/>
+    <col min="4" max="7" width="17" style="9" customWidth="1"/>
+    <col min="8" max="8" width="58.25" style="9" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="64.5" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>关卡id</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>种子名称</t>
-        </is>
-      </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>战斗id</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>所需洞府等级</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>土地庙建筑id</t>
-        </is>
-      </c>
-      <c r="G1" s="10" t="inlineStr">
-        <is>
-          <t>特殊道具id</t>
-        </is>
-      </c>
-      <c r="H1" s="10" t="inlineStr">
-        <is>
-          <t>关卡图标</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36.75" customFormat="1" customHeight="1" s="15">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>id:int</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>name:string</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>desc:string</t>
-        </is>
-      </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>combat_id:int</t>
-        </is>
-      </c>
-      <c r="E2" s="12" t="inlineStr">
-        <is>
-          <t>residence_level:int</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>building_item_id:int</t>
-        </is>
-      </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>special_item_id:int</t>
-        </is>
-      </c>
-      <c r="H2" s="12" t="inlineStr">
-        <is>
-          <t>icon:string</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16.5" customFormat="1" customHeight="1" s="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
-    </row>
-    <row r="4" ht="16.5" customFormat="1" customHeight="1" s="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" s="8">
-      <c r="A5" s="9" t="n">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="15" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+    </row>
+    <row r="4" spans="1:8" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="9">
         <v>1</v>
       </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>关卡1-1</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>关卡1</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n">
+      <c r="B5" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="9">
         <v>100080001</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="11">
         <v>1</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="11">
         <v>22070</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="9">
         <v>10509</v>
       </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>XGUI/res/round/Residence/icon/temple_01.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16.5" customHeight="1" s="8">
-      <c r="A6" s="9" t="n">
+      <c r="H5" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>关卡1-2</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>关卡2</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
+      <c r="B6" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="9">
         <v>100080002</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="11">
         <v>1</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="11">
         <v>22070</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="13">
         <v>10507</v>
       </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>XGUI/res/round/Residence/icon/temple_02.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1" s="8">
-      <c r="A7" s="9" t="n">
+      <c r="H6" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="9">
         <v>3</v>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>关卡1-3</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>关卡3</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n">
+      <c r="B7" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="9">
         <v>100080003</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="11">
         <v>1</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="11">
         <v>22070</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="9">
         <v>10508</v>
       </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>XGUI/res/round/Residence/icon/temple_03.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1" s="8">
-      <c r="A8" s="9" t="n">
+      <c r="H7" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A8" s="9">
         <v>4</v>
       </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>关卡1-4</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>关卡4</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n">
+      <c r="B8" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="9">
         <v>100080004</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="11">
         <v>1</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="11">
         <v>22070</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="13">
         <v>10511</v>
       </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>XGUI/res/round/Residence/icon/temple_04.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16.5" customHeight="1" s="8">
-      <c r="A9" s="9" t="n">
+      <c r="H8" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A9" s="9">
         <v>5</v>
       </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>关卡1-5</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>关卡5</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="n">
+      <c r="B9" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="9">
         <v>100080005</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="11">
         <v>1</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="11">
         <v>22070</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="9">
         <v>10508</v>
       </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>XGUI/res/round/Residence/icon/temple_05.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" s="8">
-      <c r="A10" s="9" t="n">
+      <c r="H9" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A10" s="9">
         <v>6</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>关卡2-1</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>关卡6</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="n">
+      <c r="B10" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="9">
         <v>100080006</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="11">
         <v>2</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="11">
         <v>22071</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="9">
         <v>10509</v>
       </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>XGUI/res/round/Residence/icon/temple_01.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" s="8">
-      <c r="A11" s="9" t="n">
+      <c r="H10" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A11" s="9">
         <v>7</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>关卡2-2</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>关卡7</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="n">
+      <c r="B11" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="9">
         <v>100080007</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="11">
         <v>2</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="11">
         <v>22071</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="13">
         <v>10511</v>
       </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>XGUI/res/round/Residence/icon/temple_02.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16.5" customHeight="1" s="8">
-      <c r="A12" s="9" t="n">
+      <c r="H11" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A12" s="9">
         <v>8</v>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>关卡2-3</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>关卡8</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="n">
+      <c r="B12" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="9">
         <v>100080008</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="11">
         <v>2</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="11">
         <v>22071</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="9">
         <v>10508</v>
       </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>XGUI/res/round/Residence/icon/temple_03.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16.5" customHeight="1" s="8">
-      <c r="A13" s="9" t="n">
+      <c r="H12" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A13" s="9">
         <v>9</v>
       </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>关卡2-4</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>关卡9</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n">
+      <c r="B13" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="9">
         <v>100080009</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="11">
         <v>2</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="11">
         <v>22071</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="13">
         <v>10511</v>
       </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>XGUI/res/round/Residence/icon/temple_04.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1" s="8">
-      <c r="A14" s="9" t="n">
+      <c r="H13" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A14" s="9">
         <v>10</v>
       </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>关卡2-5</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>关卡10</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="n">
+      <c r="B14" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="9">
         <v>100080010</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="11">
         <v>2</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="11">
         <v>22071</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="9">
         <v>10508</v>
       </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>XGUI/res/round/Residence/icon/temple_05.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>关卡3-1</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>击败聚灵塔守卫解锁更深处的灵脉</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>100090012</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>22198</v>
-      </c>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>pagoda_03.png</t>
-        </is>
-      </c>
+      <c r="H14" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G15" s="13"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A4 A15:A1048576">
-    <cfRule type="duplicateValues" priority="9" dxfId="0"/>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <conditionalFormatting sqref="A15:A1048576 A1:A4">
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" priority="10" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D14">
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F2">
-    <cfRule type="duplicateValues" priority="13" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2">
-    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>